--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +381 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +334 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +334 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +683 €/mois.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>1930</v>
+        <v>2333.33</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>

--- a/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
+++ b/docs/dossiers/dossier-paris-2eme-arrondissement-7a6d2bed.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve</t>
+          <t>loyer_estime · rendement_anormalement_eleve · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
